--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260731_tarde.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260731_tarde.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{9E549E1D-3B53-423C-BE8D-A716D9AE768E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA71003C-03FA-4274-A867-38D842DD9AC6}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{9E549E1D-3B53-423C-BE8D-A716D9AE768E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82750355-59EC-4B74-AAF3-4B0D25B0D507}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="71">
   <si>
     <t>cbo</t>
   </si>
@@ -245,49 +245,16 @@
     <t>Restricted Manoeuvrability</t>
   </si>
   <si>
-    <t>DELTA CARDINAL</t>
-  </si>
-  <si>
     <t>At Anchor</t>
   </si>
   <si>
-    <t>DELTA COMMANDER</t>
-  </si>
-  <si>
     <t>Stopped</t>
   </si>
   <si>
     <t>Moored</t>
   </si>
   <si>
-    <t>CBO ALESSANDRA</t>
-  </si>
-  <si>
-    <t>CBO ALIANCA</t>
-  </si>
-  <si>
-    <t>CBO ANITA</t>
-  </si>
-  <si>
-    <t>CBO ARPOADOR</t>
-  </si>
-  <si>
-    <t>CBO CAMPOS</t>
-  </si>
-  <si>
-    <t>CBO CAROLINA</t>
-  </si>
-  <si>
-    <t>CBO COPACABANA</t>
-  </si>
-  <si>
-    <t>CBO ENERGY</t>
-  </si>
-  <si>
-    <t>CBO FLAMENGO</t>
-  </si>
-  <si>
-    <t>CBO IPANEMA</t>
+    <t>Class B</t>
   </si>
 </sst>
 </file>
@@ -337,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -354,6 +321,15 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1025,9 +1001,7 @@
       <c r="B2" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>-22.842613</v>
       </c>
@@ -1038,7 +1012,7 @@
         <v>46234.65347222222</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1049,9 +1023,7 @@
       <c r="B3" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>-25.617207000000001</v>
       </c>
@@ -1062,7 +1034,7 @@
         <v>46232.576388888891</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1073,9 +1045,7 @@
       <c r="B4" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>-23.205189000000001</v>
       </c>
@@ -1097,9 +1067,7 @@
       <c r="B5" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>-22.881654999999999</v>
       </c>
@@ -1110,7 +1078,7 @@
         <v>46234.650694444441</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1121,9 +1089,7 @@
       <c r="B6" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>-22.864473</v>
       </c>
@@ -1134,7 +1100,7 @@
         <v>44390.56527777778</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1145,9 +1111,7 @@
       <c r="B7" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>-22.848303000000001</v>
       </c>
@@ -1158,7 +1122,7 @@
         <v>46234.652777777781</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1169,9 +1133,7 @@
       <c r="B8" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>78</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>-23.272248999999999</v>
       </c>
@@ -1193,9 +1155,7 @@
       <c r="B9" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>-22.867236999999999</v>
       </c>
@@ -1217,9 +1177,7 @@
       <c r="B10" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>-21.979752999999999</v>
       </c>
@@ -1241,9 +1199,7 @@
       <c r="B11" s="6">
         <v>46234.65902777778</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>-23.254957000000001</v>
       </c>
@@ -1262,120 +1218,220 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
-      <c r="H12" s="1"/>
+      <c r="D12" s="1">
+        <v>-22.894400000000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-43.201881</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46234.659722222219</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="6"/>
-      <c r="H13" s="1"/>
+      <c r="D13" s="1">
+        <v>-22.835771999999999</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-43.128948000000001</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46234.658333333333</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="6"/>
-      <c r="H14" s="1"/>
+      <c r="D14" s="1">
+        <v>-25.20393</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-42.877555999999998</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46232.605555555558</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="6"/>
-      <c r="H15" s="1"/>
+      <c r="D15" s="1">
+        <v>-22.891062000000002</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-43.213901999999997</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="1"/>
+      <c r="D16" s="1">
+        <v>-21.829857000000001</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-40.0867</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46233.620138888888</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="6"/>
-      <c r="H17" s="1"/>
+      <c r="D17" s="1">
+        <v>-30.372271999999999</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-47.695132999999998</v>
+      </c>
+      <c r="F17" s="6">
+        <v>44677.811111111114</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="6"/>
-      <c r="H18" s="1"/>
+      <c r="D18" s="1">
+        <v>-23.335497</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-41.314177999999998</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46233.054166666669</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="6"/>
-      <c r="H19" s="1"/>
+      <c r="D19" s="1">
+        <v>-22.864526999999999</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-43.111075999999997</v>
+      </c>
+      <c r="F19" s="6">
+        <v>45839.576388888891</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="6"/>
+      <c r="B20" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="6"/>
-      <c r="H20" s="1"/>
+      <c r="D20" s="1">
+        <v>-24.652591999999999</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-42.235106999999999</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46232.638888888891</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="6">
+        <v>46234.662499999999</v>
+      </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="6"/>
-      <c r="H21" s="1"/>
+      <c r="D21" s="1">
+        <v>-25.491667</v>
+      </c>
+      <c r="E21" s="1">
+        <v>-43.993332000000002</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46233.682638888888</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -1385,9 +1441,7 @@
       <c r="B22" s="6">
         <v>46234.652777777781</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="C22" s="1"/>
       <c r="D22" s="1">
         <v>-22.851479000000001</v>
       </c>
@@ -1398,7 +1452,7 @@
         <v>46234.647916666669</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
@@ -1410,9 +1464,7 @@
       <c r="B23" s="6">
         <v>46234.652777777781</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="C23" s="1"/>
       <c r="D23" s="1">
         <v>-22.851096999999999</v>
       </c>
@@ -1423,7 +1475,7 @@
         <v>46234.647222222222</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -1563,7 +1615,7 @@
         <v>46232.570833333331</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1585,7 +1637,7 @@
         <v>46234.655555555553</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1695,7 +1747,7 @@
         <v>46234.654166666667</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1717,7 +1769,7 @@
         <v>46234.648611111108</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1877,130 +1929,242 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="6"/>
-      <c r="H2" s="1"/>
+      <c r="D2" s="1">
+        <v>-24.609463000000002</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-42.614685000000001</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46232.760416666664</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="6"/>
+      <c r="B3" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="6"/>
-      <c r="H3" s="1"/>
+      <c r="D3" s="1">
+        <v>-24.703972</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-42.382092</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46232.588888888888</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="6"/>
-      <c r="H4" s="1"/>
+      <c r="D4" s="1">
+        <v>-22.533187999999999</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-40.152752</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46234.478472222225</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="6"/>
-      <c r="H5" s="1"/>
+      <c r="D5" s="1">
+        <v>-23.387266</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-42.956206999999999</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46233.78402777778</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="6"/>
-      <c r="H6" s="1"/>
+      <c r="D6" s="1">
+        <v>-22.43685</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-40.42503</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46233.72152777778</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="6"/>
-      <c r="H7" s="1"/>
+      <c r="D7" s="1">
+        <v>-22.822378</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-43.134219999999999</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46234.661111111112</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="B8" s="8">
+        <v>46234.664583333331</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1">
+        <v>-21.976344999999998</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-39.835574999999999</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46234.636111111111</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="6"/>
-      <c r="H9" s="1"/>
+      <c r="D9" s="1">
+        <v>-22.683430000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-40.551006000000001</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46232.838888888888</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="6"/>
-      <c r="H10" s="1"/>
+      <c r="D10" s="1">
+        <v>-22.546993000000001</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-40.068213999999998</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46234.464583333334</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="8">
+        <v>46234.664583333331</v>
+      </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="6"/>
-      <c r="H11" s="1"/>
+      <c r="D11" s="1">
+        <v>-21.93272</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-39.784393000000001</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46234.636111111111</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
-      <c r="H12" s="1"/>
+      <c r="B12" s="8">
+        <v>46234.667361111111</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7">
+        <v>-22.858196</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-43.162621000000001</v>
+      </c>
+      <c r="F12" s="8">
+        <v>46234.664583333331</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="N12" s="1"/>
     </row>
@@ -2008,11 +2172,22 @@
       <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="6"/>
-      <c r="H13" s="1"/>
+      <c r="B13" s="8">
+        <v>46234.667361111111</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7">
+        <v>-21.863316000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-41.017257999999998</v>
+      </c>
+      <c r="F13" s="8">
+        <v>46234.665277777778</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="N13" s="1"/>
     </row>
@@ -2020,55 +2195,110 @@
       <c r="A14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="6"/>
-      <c r="H14" s="1"/>
+      <c r="B14" s="8">
+        <v>46234.667361111111</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7">
+        <v>-25.79954</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-43.263905000000001</v>
+      </c>
+      <c r="F14" s="8">
+        <v>46234.502083333333</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="6"/>
-      <c r="H15" s="1"/>
+      <c r="B15" s="8">
+        <v>46234.667361111111</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7">
+        <v>-22.861601</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-43.175812000000001</v>
+      </c>
+      <c r="F15" s="8">
+        <v>46234.665277777778</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="1"/>
+      <c r="B16" s="8">
+        <v>46234.667361111111</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7">
+        <v>-22.856612999999999</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-43.166130000000003</v>
+      </c>
+      <c r="F16" s="8">
+        <v>46234.665972222225</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="6"/>
-      <c r="H17" s="1"/>
+      <c r="B17" s="8">
+        <v>46234.667361111111</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7">
+        <v>-26.856745</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-48.721401</v>
+      </c>
+      <c r="F17" s="8">
+        <v>46120.325694444444</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="6"/>
-      <c r="H18" s="1"/>
+      <c r="B18" s="8">
+        <v>46234.667361111111</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7">
+        <v>-23.373629000000001</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-42.836627999999997</v>
+      </c>
+      <c r="F18" s="9">
+        <v>46233.893055555556</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="I18" s="1"/>
     </row>
   </sheetData>

--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260731_tarde.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260731_tarde.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{9E549E1D-3B53-423C-BE8D-A716D9AE768E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82750355-59EC-4B74-AAF3-4B0D25B0D507}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{9E549E1D-3B53-423C-BE8D-A716D9AE768E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8FEE41E-1137-4449-AF80-26FCC82AB3F2}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -304,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -326,9 +326,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,15 +663,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490C43E3-ED93-4C78-B9B5-276EDD51C5AB}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -688,7 +685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -702,7 +699,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -716,7 +713,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -730,7 +727,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -744,7 +741,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -758,7 +755,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -772,7 +769,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -786,7 +783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -800,7 +797,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -814,7 +811,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -828,7 +825,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -842,7 +839,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -856,7 +853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -870,7 +867,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -884,7 +881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -895,7 +892,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -906,7 +903,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -917,7 +914,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -925,7 +922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -933,17 +930,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -956,19 +953,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DC0AFA-9444-4F11-ABC1-7475EEC3A448}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="13" max="13" width="14.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -994,7 +992,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1016,7 +1014,7 @@
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -1038,7 +1036,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1060,7 +1058,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1082,7 +1080,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1104,7 +1102,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1126,7 +1124,7 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -1148,7 +1146,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1170,7 +1168,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1192,7 +1190,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1214,7 +1212,7 @@
       </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1236,7 +1234,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -1258,7 +1256,7 @@
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1280,7 +1278,7 @@
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1302,7 +1300,7 @@
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1324,7 +1322,7 @@
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1346,7 +1344,7 @@
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1368,7 +1366,7 @@
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1390,7 +1388,7 @@
       </c>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1412,7 +1410,7 @@
       </c>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1434,7 +1432,7 @@
       </c>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1457,7 +1455,7 @@
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1479,10 +1477,10 @@
       </c>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1491,7 +1489,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1500,7 +1498,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J27" s="1"/>
     </row>
   </sheetData>
@@ -1514,20 +1512,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B80E83-9236-40C9-95ED-72F039A44EB0}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" customWidth="1"/>
-    <col min="12" max="12" width="13.21875" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" customWidth="1"/>
+    <col min="8" max="8" width="24.140625" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1553,7 +1551,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1575,7 +1573,7 @@
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1597,7 +1595,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1619,7 +1617,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1641,7 +1639,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1663,7 +1661,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1685,7 +1683,7 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1707,7 +1705,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1729,7 +1727,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1751,7 +1749,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1773,7 +1771,7 @@
       </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1795,7 +1793,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1817,7 +1815,7 @@
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1839,7 +1837,7 @@
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1861,19 +1859,19 @@
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J22" s="1"/>
     </row>
   </sheetData>
@@ -1885,21 +1883,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0244D8-3EC3-425D-A328-9D6A0DAB3C45}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" customWidth="1"/>
-    <col min="9" max="9" width="23.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1925,7 +1923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1947,7 +1945,7 @@
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1969,7 +1967,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1991,7 +1989,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -2013,7 +2011,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -2035,7 +2033,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -2057,7 +2055,7 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -2079,7 +2077,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -2101,7 +2099,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -2123,7 +2121,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -2145,7 +2143,7 @@
       </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2168,7 +2166,7 @@
       <c r="I12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -2191,7 +2189,7 @@
       <c r="I13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -2213,7 +2211,7 @@
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -2235,7 +2233,7 @@
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -2257,7 +2255,7 @@
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2279,7 +2277,7 @@
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -2293,7 +2291,7 @@
       <c r="E18" s="7">
         <v>-42.836627999999997</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>46233.893055555556</v>
       </c>
       <c r="H18" s="7" t="s">
